--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Retirement Fund - Hybrid Conservative Plan.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Retirement Fund - Hybrid Conservative Plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="138">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Retirement Fund - Hybrid Conservative Plan</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,6 +61,57 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>Ultratech Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE481G01011</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Bharti Hexacom Ltd.</t>
+  </si>
+  <si>
+    <t>INE343G01021</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>Sagar Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE229C01021</t>
+  </si>
+  <si>
+    <t>National Aluminium Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE139A01034</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
+  </si>
+  <si>
     <t>Tech Mahindra Ltd.</t>
   </si>
   <si>
@@ -70,55 +121,13 @@
     <t>It - Software</t>
   </si>
   <si>
-    <t>Ultratech Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE481G01011</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE101A01026</t>
-  </si>
-  <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
-    <t>National Aluminium Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE139A01034</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Bharti Hexacom Ltd.</t>
-  </si>
-  <si>
-    <t>INE343G01021</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>Sagar Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE229C01021</t>
+    <t>JSW Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE019A01038</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
   </si>
   <si>
     <t>Muthoot Finance Ltd.</t>
@@ -130,55 +139,46 @@
     <t>Finance</t>
   </si>
   <si>
-    <t>JSW Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE019A01038</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
+    <t>Multi Commodity Exchange Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE745G01035</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
   </si>
   <si>
     <t>Info Edge (India) Ltd.</t>
   </si>
   <si>
-    <t>INE663F01024</t>
+    <t>INE663F01032</t>
   </si>
   <si>
     <t>Retailing</t>
   </si>
   <si>
-    <t>Multi Commodity Exchange Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE745G01035</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>Titan Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE280A01028</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Wipro Ltd.</t>
-  </si>
-  <si>
-    <t>INE075A01022</t>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
+  </si>
+  <si>
+    <t>Jindal Steel &amp; Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE749A01030</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
   </si>
   <si>
     <t>Ambuja Cements Ltd.</t>
@@ -193,15 +193,36 @@
     <t>INE465A01025</t>
   </si>
   <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
     <t>Hindalco Industries Ltd.</t>
   </si>
   <si>
     <t>INE038A01020</t>
   </si>
   <si>
+    <t>UNO Minda Ltd.</t>
+  </si>
+  <si>
+    <t>INE405E01023</t>
+  </si>
+  <si>
+    <t>IndusInd Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE095A01012</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
     <t>Gland Pharma Ltd.</t>
   </si>
   <si>
@@ -211,36 +232,27 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
     <t>Jindal Stainless Ltd.</t>
   </si>
   <si>
     <t>INE220G01021</t>
   </si>
   <si>
-    <t>ICICI Prudential Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE726G01019</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
     <t>Rategain Travel Technologies Ltd.</t>
   </si>
   <si>
     <t>INE0CLI01024</t>
   </si>
   <si>
+    <t>Zee Entertainment Enterprises Ltd.</t>
+  </si>
+  <si>
+    <t>INE256A01028</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
     <t>Siemens Ltd.</t>
   </si>
   <si>
@@ -250,13 +262,10 @@
     <t>Electrical Equipment</t>
   </si>
   <si>
-    <t>Zee Entertainment Enterprises Ltd.</t>
-  </si>
-  <si>
-    <t>INE256A01028</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -271,7 +280,7 @@
     <t>Government Securities</t>
   </si>
   <si>
-    <t>IN0020230085</t>
+    <t>IN0020240126</t>
   </si>
   <si>
     <t>SOV</t>
@@ -280,19 +289,19 @@
     <t>IN0020210137</t>
   </si>
   <si>
+    <t>IN0020240035</t>
+  </si>
+  <si>
     <t>IN0020240019</t>
   </si>
   <si>
-    <t>IN0020240126</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
     <t>NABARD **</t>
   </si>
   <si>
-    <t>INE261F08DQ4</t>
+    <t>INE261F08DV4</t>
   </si>
   <si>
     <t>CRISIL AAA</t>
@@ -313,27 +322,6 @@
     <t>CRISIL AA</t>
   </si>
   <si>
-    <t>Power Finance Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE134E08HD5</t>
-  </si>
-  <si>
-    <t>Godrej Industries Ltd. **</t>
-  </si>
-  <si>
-    <t>INE233A08097</t>
-  </si>
-  <si>
-    <t>CRISIL AA+</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A08922</t>
-  </si>
-  <si>
     <t>Yes Bank Ltd. **</t>
   </si>
   <si>
@@ -346,7 +334,7 @@
     <t>Zero Coupon Bonds / Deep Discount Bonds</t>
   </si>
   <si>
-    <t>Aditya Birla Finance Ltd. **</t>
+    <t>Aditya Birla Capital Ltd. **</t>
   </si>
   <si>
     <t>INE860H07HW0</t>
@@ -424,7 +412,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -439,7 +427,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - Nifty 50 Hybrid Composite Debt 15:85 Conservative Index</t>
+    <t>Benchmark name - Nifty 50 Hybrid Composite Debt 15:85 Index</t>
   </si>
 </sst>
 </file>
@@ -817,13 +805,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -841,7 +829,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="19735800"/>
+          <a:off x="666750" y="19469100"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -856,13 +844,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -880,7 +868,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="22593300"/>
+          <a:off x="666750" y="22326600"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1214,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J112"/>
+  <dimension ref="B1:J111"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
@@ -1314,10 +1302,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>2118.73</v>
+        <v>2194.4199999999996</v>
       </c>
       <c r="H5" s="10">
-        <v>0.27873221357460004</v>
+        <v>0.2672834661133</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1351,10 +1339,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>2118.73</v>
+        <v>2194.4199999999996</v>
       </c>
       <c r="H7" s="10">
-        <v>0.27873221357460004</v>
+        <v>0.2672834661133</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1377,13 +1365,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>14665</v>
+        <v>4205</v>
       </c>
       <c r="G8" s="15">
-        <v>245.56</v>
+        <v>224.13</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0323049573875</v>
+        <v>0.0272993516556</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1409,10 +1397,10 @@
         <v>1958</v>
       </c>
       <c r="G9" s="15">
-        <v>224.92</v>
+        <v>219.49</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0295896359977</v>
+        <v>0.0267341930794</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1435,13 +1423,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>4205</v>
+        <v>10000</v>
       </c>
       <c r="G10" s="15">
-        <v>181.84</v>
+        <v>183.07</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0239221919341</v>
+        <v>0.022298185462</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1467,10 +1455,10 @@
         <v>5000</v>
       </c>
       <c r="G11" s="15">
-        <v>149.49</v>
+        <v>148.84</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0196663466357</v>
+        <v>0.0181289229484</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1490,16 +1478,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F12" s="14">
-        <v>70000</v>
+        <v>60925</v>
       </c>
       <c r="G12" s="15">
-        <v>141.57</v>
+        <v>146.29</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0186244209861</v>
+        <v>0.0178183293343</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1510,25 +1498,25 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>32</v>
-      </c>
       <c r="F13" s="14">
-        <v>10000</v>
+        <v>70000</v>
       </c>
       <c r="G13" s="15">
-        <v>135.49</v>
+        <v>126.25</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0178245588713</v>
+        <v>0.0153774289319</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1539,25 +1527,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="F14" s="14">
-        <v>60925</v>
+        <v>7481</v>
       </c>
       <c r="G14" s="15">
-        <v>126.01</v>
+        <v>117.74</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0165774054422</v>
+        <v>0.0143408988709</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1580,13 +1568,13 @@
         <v>37</v>
       </c>
       <c r="F15" s="14">
-        <v>5000</v>
+        <v>11265</v>
       </c>
       <c r="G15" s="15">
-        <v>112.94</v>
+        <v>111.92</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0148579650079</v>
+        <v>0.0136320146223</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1609,13 +1597,13 @@
         <v>40</v>
       </c>
       <c r="F16" s="14">
-        <v>11265</v>
+        <v>5000</v>
       </c>
       <c r="G16" s="15">
-        <v>106.45</v>
+        <v>110.77</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0140041648228</v>
+        <v>0.0134919429924</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1638,13 +1626,13 @@
         <v>43</v>
       </c>
       <c r="F17" s="14">
-        <v>1300</v>
+        <v>1559</v>
       </c>
       <c r="G17" s="15">
-        <v>100.41</v>
+        <v>102.93</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0132095649587</v>
+        <v>0.0125370198809</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1667,13 +1655,13 @@
         <v>46</v>
       </c>
       <c r="F18" s="14">
-        <v>1559</v>
+        <v>6500</v>
       </c>
       <c r="G18" s="15">
-        <v>89.38</v>
+        <v>92.79</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0117584993129</v>
+        <v>0.0113019535096</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1696,13 +1684,13 @@
         <v>49</v>
       </c>
       <c r="F19" s="14">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="G19" s="15">
-        <v>71.35</v>
+        <v>87.11</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0093865397849</v>
+        <v>0.0106101214595</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1722,16 +1710,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F20" s="14">
-        <v>1962</v>
+        <v>8000</v>
       </c>
       <c r="G20" s="15">
-        <v>68.48</v>
+        <v>75.91</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0090089732932</v>
+        <v>0.0092459455859</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1742,25 +1730,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F21" s="14">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="G21" s="15">
-        <v>62.38</v>
+        <v>61.25</v>
       </c>
       <c r="H21" s="16">
-        <v>0.008206480053</v>
+        <v>0.0074603368085</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1786,10 +1774,10 @@
         <v>11000</v>
       </c>
       <c r="G22" s="15">
-        <v>56.41</v>
+        <v>60.89</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0074210891278</v>
+        <v>0.0074164882983</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1809,16 +1797,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F23" s="14">
         <v>4538</v>
       </c>
       <c r="G23" s="15">
-        <v>55.55</v>
+        <v>56.31</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0073079507365</v>
+        <v>0.0068586378072</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1829,25 +1817,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>61</v>
-      </c>
       <c r="D24" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F24" s="14">
         <v>8650</v>
       </c>
       <c r="G24" s="15">
-        <v>51.41</v>
+        <v>54.80</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0067633077834</v>
+        <v>0.0066747176671</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1858,25 +1846,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="D25" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F25" s="14">
-        <v>2227</v>
+        <v>5000</v>
       </c>
       <c r="G25" s="15">
-        <v>33.96</v>
+        <v>50.33</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0044676508913</v>
+        <v>0.0061302653318</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1887,25 +1875,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>67</v>
-      </c>
       <c r="F26" s="14">
-        <v>647</v>
+        <v>5000</v>
       </c>
       <c r="G26" s="15">
-        <v>33.19</v>
+        <v>40.85</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0043663525643</v>
+        <v>0.004975587896</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1916,25 +1904,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>40</v>
-      </c>
       <c r="F27" s="14">
-        <v>5000</v>
+        <v>647</v>
       </c>
       <c r="G27" s="15">
-        <v>32.67</v>
+        <v>35.65</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0042979433044</v>
+        <v>0.0043422205261</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1945,25 +1933,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="D28" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>72</v>
-      </c>
       <c r="F28" s="14">
-        <v>2504</v>
+        <v>2227</v>
       </c>
       <c r="G28" s="15">
-        <v>15.42</v>
+        <v>35.38</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0020285976662</v>
+        <v>0.0043093341434</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1974,25 +1962,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>74</v>
-      </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F29" s="14">
-        <v>1890</v>
+        <v>5000</v>
       </c>
       <c r="G29" s="15">
-        <v>13.21</v>
+        <v>32.24</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0017378583119</v>
+        <v>0.0039268776932</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2003,25 +1991,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>76</v>
-      </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="F30" s="14">
-        <v>116</v>
+        <v>1890</v>
       </c>
       <c r="G30" s="15">
-        <v>7.05</v>
+        <v>8.39</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0009274716956</v>
+        <v>0.001021913891</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2032,25 +2020,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>78</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>80</v>
       </c>
       <c r="F31" s="14">
         <v>3400</v>
       </c>
       <c r="G31" s="15">
-        <v>3.59</v>
+        <v>4.43</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0004722870052</v>
+        <v>0.0005395802785</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2061,6 +2049,27 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" s="14">
+        <v>116</v>
+      </c>
+      <c r="G32" s="15">
+        <v>3.79</v>
+      </c>
+      <c r="H32" s="16">
+        <v>0.0004616273715</v>
+      </c>
+      <c r="I32" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J32" s="11" t="s">
@@ -2068,28 +2077,28 @@
       </c>
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I33" s="9" t="s">
+      <c r="F33" s="14">
+        <v>116</v>
+      </c>
+      <c r="G33" s="15">
+        <v>2.87</v>
+      </c>
+      <c r="H33" s="16">
+        <v>0.0003495700676</v>
+      </c>
+      <c r="I33" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J33" s="11" t="s">
@@ -2106,7 +2115,7 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>13</v>
@@ -2120,11 +2129,11 @@
       <c r="F35" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="9">
-        <v>5188.580000000001</v>
-      </c>
-      <c r="H35" s="10">
-        <v>0.6825902256137</v>
+      <c r="G35" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>85</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>13</v>
@@ -2143,7 +2152,7 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="7" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>13</v>
@@ -2158,10 +2167,10 @@
         <v>13</v>
       </c>
       <c r="G37" s="9">
-        <v>4734.550000000001</v>
+        <v>5153.6</v>
       </c>
       <c r="H37" s="10">
-        <v>0.6228597328517</v>
+        <v>0.6277157841096</v>
       </c>
       <c r="I37" s="9" t="s">
         <v>13</v>
@@ -2180,7 +2189,7 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="7" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>13</v>
@@ -2195,10 +2204,10 @@
         <v>13</v>
       </c>
       <c r="G39" s="9">
-        <v>2153.79</v>
+        <v>4744.9400000000005</v>
       </c>
       <c r="H39" s="10">
-        <v>0.2833445763629</v>
+        <v>0.5779404169229</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>13</v>
@@ -2209,57 +2218,36 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" s="17">
-        <v>7.18</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F40" s="14">
-        <v>850000</v>
-      </c>
-      <c r="G40" s="15">
-        <v>873.24</v>
-      </c>
-      <c r="H40" s="16">
-        <v>0.1148801962416</v>
-      </c>
-      <c r="I40" s="15">
-        <v>6.87</v>
+        <v>13</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" s="13" t="s">
+      <c r="B41" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="17">
-        <v>7.53</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F41" s="14">
-        <v>663030</v>
-      </c>
-      <c r="G41" s="15">
-        <v>667.86</v>
-      </c>
-      <c r="H41" s="16">
-        <v>0.0878611697379</v>
-      </c>
-      <c r="I41" s="15">
-        <v>7.47</v>
+      <c r="C41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="9">
+        <v>2930.28</v>
+      </c>
+      <c r="H41" s="10">
+        <v>0.3569122570362</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>13</v>
@@ -2267,28 +2255,28 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>88</v>
       </c>
       <c r="D42" s="17">
-        <v>7.10</v>
+        <v>6.79</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F42" s="14">
-        <v>500000</v>
+        <v>1050000</v>
       </c>
       <c r="G42" s="15">
-        <v>512.03</v>
+        <v>1087.73</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0673607563574</v>
+        <v>0.1324870556213</v>
       </c>
       <c r="I42" s="15">
-        <v>6.86</v>
+        <v>6.37</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>13</v>
@@ -2296,28 +2284,28 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C43" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="17">
+        <v>6.99</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D43" s="17">
-        <v>6.79</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>86</v>
-      </c>
       <c r="F43" s="14">
-        <v>100000</v>
+        <v>663030</v>
       </c>
       <c r="G43" s="15">
-        <v>100.66</v>
+        <v>676.80</v>
       </c>
       <c r="H43" s="16">
-        <v>0.013242454026</v>
+        <v>0.0824351992172</v>
       </c>
       <c r="I43" s="15">
-        <v>6.81</v>
+        <v>6.80</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>13</v>
@@ -2325,36 +2313,57 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>13</v>
+        <v>87</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="17">
+        <v>7.34</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F44" s="14">
+        <v>600000</v>
+      </c>
+      <c r="G44" s="15">
+        <v>638.66</v>
+      </c>
+      <c r="H44" s="16">
+        <v>0.077789693162</v>
+      </c>
+      <c r="I44" s="15">
+        <v>6.98</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="9">
-        <v>2338.7299999999996</v>
-      </c>
-      <c r="H45" s="10">
-        <v>0.3076745927305</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>13</v>
+      <c r="B45" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="17">
+        <v>7.10</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" s="14">
+        <v>500000</v>
+      </c>
+      <c r="G45" s="15">
+        <v>527.09</v>
+      </c>
+      <c r="H45" s="16">
+        <v>0.0642003090357</v>
+      </c>
+      <c r="I45" s="15">
+        <v>6.39</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>13</v>
@@ -2362,57 +2371,36 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D46" s="17">
-        <v>7.25</v>
-      </c>
-      <c r="E46" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F46" s="14">
-        <v>50</v>
-      </c>
-      <c r="G46" s="15">
-        <v>497.98</v>
-      </c>
-      <c r="H46" s="16">
-        <v>0.0655123907796</v>
-      </c>
-      <c r="I46" s="15">
-        <v>7.80</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D47" s="17">
-        <v>6.59</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F47" s="14">
-        <v>50</v>
-      </c>
-      <c r="G47" s="15">
-        <v>493.09</v>
-      </c>
-      <c r="H47" s="16">
-        <v>0.0648690806247</v>
-      </c>
-      <c r="I47" s="15">
-        <v>7.89</v>
+      <c r="C47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="9">
+        <v>1566.02</v>
+      </c>
+      <c r="H47" s="10">
+        <v>0.19074345549349997</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>13</v>
@@ -2420,28 +2408,28 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" s="17">
+        <v>7.62</v>
+      </c>
+      <c r="E48" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D48" s="17">
-        <v>8.50</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>98</v>
-      </c>
       <c r="F48" s="14">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="G48" s="15">
-        <v>352.88</v>
+        <v>511.67</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0464235761643</v>
+        <v>0.0623221311812</v>
       </c>
       <c r="I48" s="15">
-        <v>8.04</v>
+        <v>6.61</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>13</v>
@@ -2449,28 +2437,28 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D49" s="17">
-        <v>8.39</v>
+        <v>6.59</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F49" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G49" s="15">
-        <v>300.39</v>
+        <v>499.57</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0395181876105</v>
+        <v>0.0608483340321</v>
       </c>
       <c r="I49" s="15">
-        <v>7.69</v>
+        <v>6.85</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>13</v>
@@ -2478,28 +2466,28 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="17">
+        <v>8.50</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D50" s="17">
-        <v>7.17</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>103</v>
-      </c>
       <c r="F50" s="14">
-        <v>30</v>
+        <v>350</v>
       </c>
       <c r="G50" s="15">
-        <v>298.98</v>
+        <v>355.83</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0393326932714</v>
+        <v>0.0433405983118</v>
       </c>
       <c r="I50" s="15">
-        <v>8.03</v>
+        <v>7.40</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>13</v>
@@ -2507,28 +2495,28 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D51" s="17">
+        <v>8</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D51" s="17">
-        <v>7.80</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>93</v>
-      </c>
       <c r="F51" s="14">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="G51" s="15">
-        <v>199.64</v>
+        <v>198.95</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0262638935203</v>
+        <v>0.0242323919684</v>
       </c>
       <c r="I51" s="15">
-        <v>7.95</v>
+        <v>8.38</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>13</v>
@@ -2536,65 +2524,65 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="15" customHeight="1">
+      <c r="B53" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="9">
+        <v>248.64</v>
+      </c>
+      <c r="H53" s="10">
+        <v>0.0302847043932</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="15" customHeight="1">
+      <c r="B54" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C54" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D52" s="17">
-        <v>8</v>
-      </c>
-      <c r="E52" s="13" t="s">
+      <c r="D54" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="F52" s="14">
+      <c r="F54" s="14">
         <v>20</v>
       </c>
-      <c r="G52" s="15">
-        <v>195.77</v>
-      </c>
-      <c r="H52" s="16">
-        <v>0.0257547707597</v>
-      </c>
-      <c r="I52" s="15">
-        <v>9.38</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="9">
-        <v>242.03</v>
-      </c>
-      <c r="H54" s="10">
-        <v>0.0318405637583</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>13</v>
+      <c r="G54" s="15">
+        <v>248.64</v>
+      </c>
+      <c r="H54" s="16">
+        <v>0.0302847043932</v>
+      </c>
+      <c r="I54" s="15">
+        <v>7</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>13</v>
@@ -2602,102 +2590,102 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="15" customHeight="1">
+      <c r="B56" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="15" customHeight="1">
+      <c r="B57" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="15" customHeight="1">
+      <c r="B58" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="9">
+        <v>408.66</v>
+      </c>
+      <c r="H58" s="10">
+        <v>0.0497753671867</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="15" customHeight="1">
+      <c r="B59" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D55" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="13" t="s">
+      <c r="C59" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="F55" s="14">
-        <v>20</v>
-      </c>
-      <c r="G55" s="15">
-        <v>242.03</v>
-      </c>
-      <c r="H55" s="16">
-        <v>0.0318405637583</v>
-      </c>
-      <c r="I55" s="15">
-        <v>8.03</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" ht="15" customHeight="1">
-      <c r="B56" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" ht="15" customHeight="1">
-      <c r="B57" s="7" t="s">
+      <c r="D59" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" ht="15" customHeight="1">
-      <c r="B58" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="9">
-        <v>454.03</v>
-      </c>
-      <c r="H59" s="10">
-        <v>0.059730492762</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>13</v>
+      <c r="F59" s="14">
+        <v>2</v>
+      </c>
+      <c r="G59" s="15">
+        <v>194.62</v>
+      </c>
+      <c r="H59" s="16">
+        <v>0.0237049918316</v>
+      </c>
+      <c r="I59" s="15">
+        <v>7.76</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>13</v>
@@ -2705,28 +2693,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F60" s="14">
         <v>2</v>
       </c>
       <c r="G60" s="15">
-        <v>196.97</v>
+        <v>122.31</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0259126382823</v>
+        <v>0.0148975313478</v>
       </c>
       <c r="I60" s="15">
-        <v>8.32</v>
+        <v>7.39</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>13</v>
@@ -2734,28 +2722,28 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C61" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C61" s="13" t="s">
-        <v>118</v>
-      </c>
       <c r="D61" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F61" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" s="15">
-        <v>161.41</v>
+        <v>91.73</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0212344973608</v>
+        <v>0.0111728440073</v>
       </c>
       <c r="I61" s="15">
-        <v>8.34</v>
+        <v>7.52</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>13</v>
@@ -2763,377 +2751,377 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C62" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" ht="15" customHeight="1">
+      <c r="B63" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="15" customHeight="1">
+      <c r="B64" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="15" customHeight="1">
+      <c r="B65" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="15" customHeight="1">
+      <c r="B66" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="15" customHeight="1">
+      <c r="B67" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" ht="15" customHeight="1">
+      <c r="B68" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" ht="15" customHeight="1">
+      <c r="B69" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D62" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F62" s="14">
-        <v>1</v>
-      </c>
-      <c r="G62" s="15">
-        <v>95.65</v>
-      </c>
-      <c r="H62" s="16">
-        <v>0.0125833571189</v>
-      </c>
-      <c r="I62" s="15">
-        <v>8.34</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" ht="15" customHeight="1">
-      <c r="B63" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" ht="15" customHeight="1">
-      <c r="B64" s="7" t="s">
+      <c r="C69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" ht="15" customHeight="1">
+      <c r="B70" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" ht="15" customHeight="1">
+      <c r="B71" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" ht="15" customHeight="1">
-      <c r="B65" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" ht="15" customHeight="1">
-      <c r="B66" s="7" t="s">
+      <c r="C71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="15" customHeight="1">
+      <c r="B72" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" ht="15" customHeight="1">
+      <c r="B73" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" ht="15" customHeight="1">
-      <c r="B67" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" ht="15" customHeight="1">
-      <c r="B68" s="7" t="s">
+      <c r="C73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="15" customHeight="1">
+      <c r="B74" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="15" customHeight="1">
+      <c r="B75" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C68" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I68" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J68" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" ht="15" customHeight="1">
-      <c r="B69" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" ht="15" customHeight="1">
-      <c r="B70" s="7" t="s">
+      <c r="C75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="15" customHeight="1">
+      <c r="B76" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="15" customHeight="1">
+      <c r="B77" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C70" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I70" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J70" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" ht="15" customHeight="1">
-      <c r="B71" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" ht="15" customHeight="1">
-      <c r="B72" s="7" t="s">
+      <c r="C77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="15" customHeight="1">
+      <c r="B78" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="15" customHeight="1">
+      <c r="B79" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C72" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H72" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I72" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J72" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" ht="15" customHeight="1">
-      <c r="B73" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" ht="15" customHeight="1">
-      <c r="B74" s="7" t="s">
+      <c r="C79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="9">
+        <v>805.80</v>
+      </c>
+      <c r="H79" s="10">
+        <v>0.0981475820467</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15" customHeight="1">
+      <c r="B80" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1">
+      <c r="B81" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="C74" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" ht="15" customHeight="1">
-      <c r="B75" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J76" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" ht="15" customHeight="1">
-      <c r="B77" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J77" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" ht="15" customHeight="1">
-      <c r="B78" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" ht="15" customHeight="1">
-      <c r="B79" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="9">
-        <v>142.06</v>
-      </c>
-      <c r="H80" s="10">
-        <v>0.0186888835578</v>
-      </c>
-      <c r="I80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="11" t="s">
+      <c r="C81" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="19">
+        <v>56.26509018999968</v>
+      </c>
+      <c r="H81" s="20">
+        <v>0.006853167728703477</v>
+      </c>
+      <c r="I81" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="18" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C82" s="19" t="s">
         <v>13</v>
@@ -3148,10 +3136,10 @@
         <v>13</v>
       </c>
       <c r="G82" s="19">
-        <v>151.94013497999913</v>
+        <v>8210.08509019</v>
       </c>
       <c r="H82" s="20">
-        <v>0.01998867725193782</v>
+        <v>0.9999999999983034</v>
       </c>
       <c r="I82" s="19" t="s">
         <v>13</v>
@@ -3160,38 +3148,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C83" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="19">
-        <v>7601.31013498</v>
-      </c>
-      <c r="H83" s="20">
-        <v>0.9999999999980379</v>
-      </c>
-      <c r="I83" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9" ht="15" customHeight="1">
+    <row r="85" spans="2:9" ht="15" customHeight="1">
+      <c r="B85" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C85" s="22"/>
+      <c r="D85" s="22"/>
+      <c r="E85" s="22"/>
+      <c r="F85" s="22"/>
+      <c r="G85" s="22"/>
+      <c r="H85" s="22"/>
+      <c r="I85" s="22"/>
+    </row>
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="13" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C86" s="22"/>
       <c r="D86" s="22"/>
@@ -3199,11 +3170,10 @@
       <c r="F86" s="22"/>
       <c r="G86" s="22"/>
       <c r="H86" s="22"/>
-      <c r="I86" s="22"/>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="13" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C87" s="22"/>
       <c r="D87" s="22"/>
@@ -3214,7 +3184,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="13" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C88" s="22"/>
       <c r="D88" s="22"/>
@@ -3223,9 +3193,9 @@
       <c r="G88" s="22"/>
       <c r="H88" s="22"/>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
-      <c r="B89" s="13" t="s">
-        <v>134</v>
+    <row r="89" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B89" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="C89" s="22"/>
       <c r="D89" s="22"/>
@@ -3236,7 +3206,7 @@
     </row>
     <row r="90" spans="2:8" ht="27.6" customHeight="1">
       <c r="B90" s="23" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C90" s="22"/>
       <c r="D90" s="22"/>
@@ -3247,7 +3217,7 @@
     </row>
     <row r="91" spans="2:8" ht="27.6" customHeight="1">
       <c r="B91" s="23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C91" s="22"/>
       <c r="D91" s="22"/>
@@ -3256,55 +3226,44 @@
       <c r="G91" s="22"/>
       <c r="H91" s="22"/>
     </row>
-    <row r="92" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B92" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22"/>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="22"/>
-      <c r="H92" s="22"/>
-    </row>
-    <row r="93" spans="2:7" ht="63" customHeight="1">
-      <c r="B93" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="C93" s="24"/>
-      <c r="D93" s="24"/>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-    </row>
-    <row r="96" ht="15">
-      <c r="B96" s="22" t="s">
-        <v>139</v>
+    <row r="92" spans="2:7" ht="57" customHeight="1">
+      <c r="B92" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="C92" s="24"/>
+      <c r="D92" s="24"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+    </row>
+    <row r="95" ht="15">
+      <c r="B95" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="110" ht="15">
+      <c r="B110" s="22" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="111" ht="15">
       <c r="B111" s="22" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="112" ht="15">
-      <c r="B112" s="22" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B93:G93"/>
+    <mergeCell ref="B92:G92"/>
+    <mergeCell ref="B87:H87"/>
     <mergeCell ref="B88:H88"/>
     <mergeCell ref="B89:H89"/>
     <mergeCell ref="B90:H90"/>
     <mergeCell ref="B91:H91"/>
-    <mergeCell ref="B92:H92"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B86:I86"/>
-    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="B85:I85"/>
+    <mergeCell ref="B86:H86"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
